--- a/data/daily/2026-09/2026-09-19.xlsx
+++ b/data/daily/2026-09/2026-09-19.xlsx
@@ -1170,14 +1170,39 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1192,17 +1217,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>2</row>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1292,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1342,42 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,110 +1392,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="352425" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>10</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1425,52 +1425,102 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,179 +1528,129 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>10</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="952500" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId9"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>11</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -2596,21 +2596,21 @@
         <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>16081</v>
+        <v>16084</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>피로 회복 및 에너지 충전 — 피로할 때 먹으면 빠르게 에너지가 보충되고 컨디션이 회복됨</t>
+          <t>고급스러운 선물 포장 — 포장이 럭셔리하고 완성도가 높아 명절이나 기념일 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>고급스러운 명절 선물용 — 선물 포장이 잘되어 있고 명절 선물로 주고받기 좋음</t>
+          <t>피로 회복 및 컨디션 개선 — 야근이나 피로 누적 시 섭취하면 활력과 면역력 증진에 효과적임</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>알찬 패키지와 샘플 증정 — 보너스 1입과 추가 샘플 구성으로 알찬 느낌을 줌</t>
+          <t>알찬 보너스 구성 및 편한 섭취 — 추가 보너스 입수가 포함되어 있으며 액상과 정제 조합으로 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2655,21 +2655,21 @@
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>15420</v>
+        <v>15422</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 방식 — 마시는 액상과 알약이 통합되어 손에 묻지 않고 섭취하기 편리함</t>
+          <t>피로 해소 및 활력 증진 — 지치고 피곤할 때 섭취하면 컨디션 회복과 활력에 큰 도움이 됨</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 패키지 — 패키지 디자인이 고급스럽고 GMP 인증이 있어 선물용으로 적합함</t>
+          <t>편리한 올인원 앰플 제형 — 알약과 마시는 액상이 하나로 결합되어 손에 묻히지 않고 간편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>알찬 추가 1입 증정 구성 — 10입에 1입이 추가 증정되어 알찬 구성으로 만족스러움</t>
+          <t>고급스러운 패키지와 증정 구성 — 추석 선물 패키지의 포장이 고급스럽고 추가 증정 구성이 포함되어 훌륭함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -2714,22 +2714,22 @@
         <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 섭취 후 피로감이 줄어들고 에너지 충전에 도움이 됨</t>
+          <t>피로 회복 및 체력 증진 — 체력이 떨어졌을 때 피로감을 줄여주고 에너지를 보충해 줌</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>감동을 주는 고급 선물 — 고급스러운 제품 구성으로 생일이나 명절 선물용으로 만족도가 높음</t>
+          <t>선물하기 좋은 고급 케이스 — 케이스 디자인이 고급스러워 명절이나 생일 선물용으로 만족도가 높음</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 수령 직후 판매 가격이 내려가 아쉬움이 남음</t>
+          <t>구매 직후 가격 하락 — 제품 구매 후 가격이 추가 할인되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2773,19 +2773,23 @@
         <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>8706</v>
+        <v>8707</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>신속한 활력 충전 효과 — 피로할 때 먹으면 효과가 빠르게 나타나며 활력이 생김</t>
+          <t>빠른 피로 회복 효과 — 섭취 후 즉각적인 에너지 충전과 피로 개선 체감이 뛰어남</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>부담 없는 실용적 선물 — 매일 간편하게 챙겨 먹기 좋아 주고받는 선물로 실용적임</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>간편한 일상 섭취 — 바쁜 날에도 부담 없이 챙겨 먹기 좋고 간편함</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>푸짐한 서비스 증정 — 추가 증정 구성품이 함께 제공되어 만족스러움</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
@@ -2832,17 +2836,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 작은 정제 크기 — 정제 크기가 크지 않아 알약을 잘 못 넘기는 사람도 쉽게 섭취 가능함</t>
+          <t>확실한 컨디션 회복 — 피로가 쌓였을 때 섭취하면 빠르게 컨디션을 회복하고 힘이 남</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>신속한 컨디션 회복 — 피로할 때 섭취 시 활력이 생기고 컨디션 회복에 도움이 됨</t>
+          <t>작은 정제로 편한 목넘김 — 알약 크기가 크지 않아 목으로 넘기기 용이함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>정성스럽고 고급스러운 포장 — 포장 상태가 고급스러워 선물용으로 만족도가 높음</t>
+          <t>선물용으로 우수한 패키지 — 포장 상태가 깔끔하고 고급스러워 생일 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -2860,47 +2864,51 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>센트룸</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24,000원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7320451</t>
+          <t>https://gift.kakao.com/product/10903147</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>6478</v>
+        <v>749</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>물 없이 먹는 젤리 타입 — 구미 형태라 물 없이 간편하게 섭취할 수 있어 매일 챙기기 쉬움</t>
+          <t>체력 유지 및 피로 회복 — 운동 후나 야근 시 섭취하면 컨디션 회복과 훈련 집중도 향상에 도움 됨</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>맛있고 향긋한 풍미 — 맛과 향이 좋아 거부감 없이 맛있게 먹을 수 있음</t>
+          <t>대용량 및 사은품 증정 — 30병의 넉넉한 양에 레몬샷 증정품까지 제공되어 알참</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>배송 시 제품 박스 훼손 — 배송 중 포장 박스가 찢어져서 도착함</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
@@ -2915,51 +2923,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+          <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>센트룸</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>52,900원</t>
+          <t>24,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/10903147</t>
+          <t>https://gift.kakao.com/product/7320451</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260601193534_8d89165f65364cb0b3c77a98481c17d6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260901110153_bb9a8b1870e2492e99dbbf1747444c66.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>749</v>
+        <v>6478</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>체력 관리 및 피로 회복 — 복용 후 피로가 줄고 컨디션과 훈련 집중도 유지에 도움이 됨</t>
+          <t>맛있고 간편한 구미 제형 — 물 없이 간식처럼 섭취할 수 있고 쫄깃하며 맛이 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>대용량 구성 및 혜택 — 30병 대용량에 증정품까지 추가되어 든든함</t>
+          <t>귀여운 포장 및 외관 — 제품 포장과 모양이 예뻐 부담 없이 선물하기에 좋음</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>배송 중 박스 훼손 — 배송 과정에서 제품 박스가 찢어진 상태로 전달됨</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
@@ -3005,17 +3009,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 패키지 — 포장이 깔끔하고 고급스러워 가볍게 선물하기에 적합함</t>
+          <t>고급스러운 포장 디자인 — 패키지 포장이 정성스럽고 고급스러워 선물용으로 제격임</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>새콤달콤하여 맛있는 맛 — 새콤하고 달콤한 오렌지 맛으로 맛있게 먹을 수 있음</t>
+          <t>새콤달콤 맛있는 액상 — 오렌지 맛의 새콤달콤한 액상으로 거부감 없이 간편하게 복용 가능함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>간편한 복용 및 피로 감소 — 복용 방식이 간편하고 마신 후 피로감이 줄어드는 느낌임</t>
+          <t>피로 감소 및 체력 회복 — 섭취 후 피로함이 줄어들고 활기찬 기분을 주는 데 도움 됨</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -3060,21 +3064,21 @@
         <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>29549</v>
+        <v>29552</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>맛있는 액상과 비타민 젤리 — 맛이 새콤하고 개운하며 함께 증정된 비타민 젤리도 맛있음</t>
+          <t>간편한 휴대 및 올인원 섭취 — 한 병에 알약과 액상이 같이 있어 가방에 휴대하며 먹기 편리함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>한 병으로 간편한 영양 보충 — 하루 한 병과 정제로 여러 영양소를 간편하고 휴대하기 쉽게 챙김</t>
+          <t>개운한 맛과 편안한 속 — 맛이 새콤하고 개운하며 복용 후 속이 불편하지 않음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>속 더부룩함 없는 편안함 — 알약 크기가 적당하고 섭취 후 속이 불편한 느낌이 없음</t>
+          <t>고급 포장과 젤리 증정 — 포장이 깔끔하고 추가 동봉된 비타민 젤리가 맛있음</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -3084,7 +3088,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -3092,51 +3096,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
+          <t>'1입 추가 증정' "성별 맞춤 설계" 오쏘몰 바이탈 m/f 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>오쏘몰</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/5551542</t>
+          <t>https://gift.kakao.com/product/8167919</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260513082713_f5025425b9024348b2621639f67a34af.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260907084156_6695f5fa3b10400983a93ac3be43afb0.jpg</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>2621</v>
+        <v>770</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 피로가 쌓였을 때 마시면 피로감이 줄어들고 몸에 활력이 생김</t>
+          <t>성별 맞춤 영양 설계 — 남성과 여성에 맞는 영양소로 구성되어 효율적인 관리가 가능함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>맛있는 액상 비타민 — 섭취하기에 맛이 좋아 부담 없이 먹기 편함</t>
+          <t>지속적인 활력 및 피로 완화 — 꾸준히 복용 시 피로가 감소하고 활력이 오래 지속됨</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>고급스러운 패키지와 증정품 — 추석 선물 패키지가 고급스럽고 젤리까지 추가되어 만족스러움</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>선물 느낌의 깔끔한 포장 — 포장이 정성스럽고 깔끔하여 선물 받는 기분을 북돋아 줌</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>큰 알약 크기로 인한 불편 — 정제 크기가 커서 물로 삼킬 때 다소 부담스러움</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -3182,20 +3190,24 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>매우 고급스러운 선물 포장 — 틴케이스, 보자기 등 핑크톤 포장이 섬세하고 고급스러움</t>
+          <t>정성스럽고 고급스러운 포장 — 보자기, 틴케이스, 핑크 박스 등 포장 구성이 예쁘고 고급스러움</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>비리지 않고 맛있는 맛 — 비린 맛 없이 맛있게 먹을 수 있음</t>
+          <t>비리지 않고 맛있는 액상 — 콜라겐 특유의 비린 맛이 없고 맛이 뛰어남</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>피부 변화 및 만족도 — 섭취 후 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>피부 개선 체감 효과 — 섭취 시 피부가 맑아지고 탱탱해지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>지속적인 가격 상승 — 제품 가격이 계속 인상되어 부담이 생김</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3241,18 +3253,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>소화 및 변비 개선 효과 — 속 거북함이 줄어들고 변비 증상이 개선되어 지속 복용함</t>
+          <t>소화 및 변비 개선 효과 — 소화 불량을 완화하고 변비 증상 개선에 큰 도움이 됨</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>풍성한 구성과 저렴한 가격 — 덤 증정품과 함께 저렴한 가격으로 구매할 수 있어 만족스러움</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>합리적인 가격과 사은품 — 가격이 착하고 추가 효소 사은품까지 풍성하게 증정됨</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>고급스러운 선물 포장 — 선물 포장 상태가 깔끔하고 고급스러움</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 아쉬움 — 지인 선물용으로 여러 개 구매하고 싶으나 구매 갯수 제한이 있음</t>
+          <t>구매 수량 제한의 아쉬움 — 지인 선물용으로 구매 시 수량 제한이 있어 불편함</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3261,7 +3277,7 @@
     <row r="14" ht="38" customHeight="1">
       <c r="B14" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3269,49 +3285,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>한끼통살</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>19,900원</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/11566779</t>
+          <t>https://gift.kakao.com/product/13180362</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>147</v>
+        <v>875</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>다양하고 맛있는 메뉴 구성 — 여러 가지 맛이 있어 질리지 않고 간편하게 먹을 수 있음</t>
+          <t>뛰어난 소화 촉진 효과 — 식후 복용 시 소화가 잘 되며 소화력이 떨어진 사람에게 추천함</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>실용적인 보냉백 증정 — 함께 증정되는 보냉파우치(도시락가방)가 유용함</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
+          <t>우수한 가성비 — 저렴한 가격에 많은 수량을 구매할 수 있어 경제적임</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>빠른 배송 및 예쁜 패키지 — 배송이 빠르고 선물하기 좋은 예쁜 포장으로 도착함</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>배송 중 포장 터짐 문제 — 일부 제품의 진공 포장이 헐렁하거나 터져서 소스가 흘러나옴</t>
+          <t>구매 갯수 제한 존재 — 대량 구매 시 갯수 제한이 설정되어 있어 아쉬움</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3320,7 +3340,7 @@
     <row r="15" ht="38" customHeight="1">
       <c r="B15" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -3328,52 +3348,56 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
+          <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>한끼통살</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/14208051</t>
+          <t>https://gift.kakao.com/product/11566779</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260429112212_3e1db89ad7174b6989286381ae7257c6.jpg</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>93</v>
+        <v>147</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>기대를 뛰어넘는 맛있는 맛 — 말차를 잘 못 먹는 사람도 맛있게 먹을 수 있는 풍미임</t>
+          <t>다채롭고 맛있는 종류 구성 — 다양한 맛으로 구성되어 질리지 않고 맛있게 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>포토카드와 단백질바 사은품 — 리센느 원이 포토카드와 단백질 스낵이 함께 들어있어 만족스러움</t>
+          <t>알찬 가성비 및 보냉백 증정 — 가격 대비 양이 많고 도시락용 보냉 파우치를 함께 증정함</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>포토카드 무작위 구성 미적용 — 포토카드가 랜덤 구성이 아닌 고정형으로 제공되어 아쉬움</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
+          <t>포장 불량으로 인한 터짐 — 진공 포장이 헐렁하거나 봉지가 터져 소스가 묻어남</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>증정 가방 크기 차이 — 사은품으로 받은 도시락 가방이 사진보다 실제 크기가 큼</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr"/>
     </row>
     <row r="16" ht="38" customHeight="1">
@@ -3387,7 +3411,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+          <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3397,39 +3421,39 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19,900원</t>
+          <t>24,900원</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180362</t>
+          <t>https://gift.kakao.com/product/14208051</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260911094744_fdcb15f83b684390b6fd43416e90d400.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260908134122_cb4724fa4d2d4e45b370faede2a463a5.jpg</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>4</v>
       </c>
       <c r="J16" t="n">
-        <v>875</v>
+        <v>93</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>우수한 소화 촉진 효과 — 식후 복용 시 소화가 잘 되어 소화력 개선에 큰 도움이 됨</t>
+          <t>거부감 없는 맛있는 말차 맛 — 말차를 잘 못 먹는 사람도 맛있게 먹을 수 있으며 섭취가 간편함</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>가성비 좋은 저렴한 가격 — 증정품 포함 알찬 구성을 저렴하게 구매할 수 있음</t>
+          <t>알찬 굿즈 및 사은품 — 포토카드와 단백질 바 증정 등 에디션 구성이 풍성함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 불편함 — 선물용으로 대량 구매를 원하나 개수 제한이 설정되어 있음</t>
+          <t>포토카드 구성의 아쉬움 — 포토카드가 고정 디자인으로 제공되어 다소 아쉬움</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3477,18 +3501,18 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>부드러운 식감과 뛰어난 맛 — 닭가슴살 특유의 뻑뻑함이 없고 맛이 자극적이지 않음</t>
+          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 뻑뻑하지 않고 부드러우며 다채로운 양념으로 물리지 않음</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>매일 색다른 다양성 — 맛의 종류가 다채로워 다이어트 중에도 물리지 않음</t>
+          <t>저렴한 가격과 간편한 조리 — 구성 대비 가격이 착하고 전자레인지 조리로 간편함</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 상태 — 배송 과정에서 상품이 전부 녹은 상태로 수령됨</t>
+          <t>배송 시 제품 해동 상태 — 배송 과정에서 제품이 완전히 녹아서 도착함</t>
         </is>
       </c>
       <c r="O17" t="inlineStr"/>
@@ -3536,17 +3560,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>텁텁함 없는 달콤한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛 없이 진하고 달콤함</t>
+          <t>비린 맛 없는 달콤한 풍미 — 단백질 음료 특유의 텁텁함이나 비린 맛이 전혀 없고 맛있음</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>속 편한 부드러운 목넘김 — 마신 후 속이 더부룩하지 않고 부드럽게 마실 수 있음</t>
+          <t>부드러운 목넘김과 속 편안함 — 당이 낮고 부드러우며 마신 뒤 속 더부룩함이 적음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>휴대하기 편리한 디자인 — 슬림한 팩 형태로 가방에 들고 다니며 챙겨 마시기 편함</t>
+          <t>휴대하기 편한 패키지 — 패키지가 슬림하여 가방에 휴대하며 운동 후나 간식으로 먹기 좋음</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3595,17 +3619,25 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>고급스러운 앰플 용기 디자인 — 용기와 포장이 고급스러워 공주님이 먹는 듯한 느낌을 줌</t>
+          <t>고급스럽고 예쁜 패키지 — 케이스와 병 디자인이 공주풍으로 예쁘고 고급스러워 선물용으로 좋음</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>먹기 편한 맛있는 풍미 — 맛이 있어 약 같은 거부감 없이 즐겁게 마실 수 있음</t>
+          <t>상큼하고 거부감 없는 맛 — 비타민 음료처럼 상큼하고 맛있어서 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>진한 농도로 인한 섭취 느낌 — 액상이 다소 진하여 마신 후 물을 따로 마셔야 함</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>단기 복용 시 미미한 효과 — 짧은 기간 복용 시에는 체감되는 효과가 다소 부족함</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr"/>
     </row>
     <row r="20" ht="38" customHeight="1">
@@ -3650,17 +3682,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6200mg 초고함량 활력 제공 — 아르기닌 함량이 높아 운동 시 지구력과 활력 충전에 효과적임</t>
+          <t>초고함량으로 뛰어난 활력 제공 — 6200mg 고함량이라 운동 시 지구력 향상과 피로 회복에 효과적임</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>고급 선물 패키지와 추가 증정 — 전용 쇼핑백과 추가 5포 증정으로 선물용 완성도가 높음</t>
+          <t>휴대 및 섭취의 간편성 — 하루 1포 개별 포장으로 휴대 및 복용이 편함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>하루 1포 간편한 개별 포장 — 개별 포장되어 있어 가지고 다니며 언제든 먹기 편리함</t>
+          <t>고급 포장과 추가 증정 — 전용 쇼핑백과 추가 증정 포가 구성되어 선물하기에 적합함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3678,48 +3710,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>뉴트리디데이</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>30,900원</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/7556791</t>
+          <t>https://gift.kakao.com/product/4487367</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260904160657_c66395adeecf4b11a3a2afd7f4e2d479.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260727151443_bd470867f85f4a79857e43d8b82ff835.jpg</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>1534</v>
+        <v>39</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>아르기닌과 밀크씨슬의 조합 — 활력과 간 건강을 한 번에 챙길 수 있는 영양제 구성임</t>
+          <t>피로 회복 및 운동 체력 증진 — 복용 시 하루를 가볍게 시작할 수 있고 운동 수행 능력 향상에 도움 됨</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>피로 개선 및 체력 증진 — 아침에 일어날 때 몸이 가벼워지고 운동 수행 능력에 도움이 됨</t>
+          <t>부담 없는 상큼한 레몬 맛 — 맛있는 레몬 맛이라 거부감 없이 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>넉넉한 용량과 선물용 구성 — 2개월 분량에 쇼핑백까지 증정되어 선물하기에 적합함</t>
+          <t>외출 시 편한 액상 스틱 — 액상 스틱 제형이라 물 없이도 챙겨 먹기 쉽고 외출 시 휴대하기 용이함</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3882,7 +3914,7 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
     </row>
@@ -3919,14 +3951,14 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
           <t>센트룸</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>정관장</t>
@@ -3939,7 +3971,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>오쏘몰</t>
         </is>
       </c>
     </row>
@@ -3976,14 +4008,14 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
+          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>[센트룸] 맛있는 멀티비타민 미네랄 멀티구미 (80구미)</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>"올인원 명품비타민" 이뮨비타민 올인원 멀티비타민&amp;미네랄 프로 30병+쇼핑백증정</t>
-        </is>
-      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
           <t>신상비타민선물 [정관장] 활기마이트(액상30ml+분말500mg) 7입 + [증정] 1입</t>
@@ -3996,7 +4028,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>비타민 선물 추천 아임비타 멀티비타민 이뮨샷 1박스(5입) / 비타민선물 응원선물 에너지 선물 직장동료 선물</t>
+          <t>'1입 추가 증정' "성별 맞춤 설계" 오쏘몰 바이탈 m/f 14+1입 - 시그니처 기프트 에디션 (공식수입)</t>
         </is>
       </c>
     </row>
@@ -4044,34 +4076,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>16081</v>
+        <v>16084</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>15420</v>
+        <v>15422</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3353</v>
+        <v>3354</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>8706</v>
+        <v>8707</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>788</v>
       </c>
       <c r="H7" s="3" t="n">
+        <v>749</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>6478</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>749</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>1650</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>29549</v>
+        <v>29552</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>2621</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -4082,68 +4114,69 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 에너지 충전 — 피로할 때 먹으면 빠르게 에너지가 보충되고 컨디션이 회복됨
-고급스러운 명절 선물용 — 선물 포장이 잘되어 있고 명절 선물로 주고받기 좋음
-알찬 패키지와 샘플 증정 — 보너스 1입과 추가 샘플 구성으로 알찬 느낌을 줌</t>
+          <t>고급스러운 선물 포장 — 포장이 럭셔리하고 완성도가 높아 명절이나 기념일 선물용으로 적합함
+피로 회복 및 컨디션 개선 — 야근이나 피로 누적 시 섭취하면 활력과 면역력 증진에 효과적임
+알찬 보너스 구성 및 편한 섭취 — 추가 보너스 입수가 포함되어 있으며 액상과 정제 조합으로 챙겨 먹기 편함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간편한 올인원 섭취 방식 — 마시는 액상과 알약이 통합되어 손에 묻지 않고 섭취하기 편리함
-고급스러운 선물용 패키지 — 패키지 디자인이 고급스럽고 GMP 인증이 있어 선물용으로 적합함
-알찬 추가 1입 증정 구성 — 10입에 1입이 추가 증정되어 알찬 구성으로 만족스러움</t>
+          <t>피로 해소 및 활력 증진 — 지치고 피곤할 때 섭취하면 컨디션 회복과 활력에 큰 도움이 됨
+편리한 올인원 앰플 제형 — 알약과 마시는 액상이 하나로 결합되어 손에 묻히지 않고 간편하게 먹을 수 있음
+고급스러운 패키지와 증정 구성 — 추석 선물 패키지의 포장이 고급스럽고 추가 증정 구성이 포함되어 훌륭함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 회복 효과 — 섭취 후 피로감이 줄어들고 에너지 충전에 도움이 됨
-감동을 주는 고급 선물 — 고급스러운 제품 구성으로 생일이나 명절 선물용으로 만족도가 높음</t>
+          <t>피로 회복 및 체력 증진 — 체력이 떨어졌을 때 피로감을 줄여주고 에너지를 보충해 줌
+선물하기 좋은 고급 케이스 — 케이스 디자인이 고급스러워 명절이나 생일 선물용으로 만족도가 높음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>신속한 활력 충전 효과 — 피로할 때 먹으면 효과가 빠르게 나타나며 활력이 생김
-부담 없는 실용적 선물 — 매일 간편하게 챙겨 먹기 좋아 주고받는 선물로 실용적임</t>
+          <t>빠른 피로 회복 효과 — 섭취 후 즉각적인 에너지 충전과 피로 개선 체감이 뛰어남
+간편한 일상 섭취 — 바쁜 날에도 부담 없이 챙겨 먹기 좋고 간편함
+푸짐한 서비스 증정 — 추가 증정 구성품이 함께 제공되어 만족스러움</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>삼키기 쉬운 작은 정제 크기 — 정제 크기가 크지 않아 알약을 잘 못 넘기는 사람도 쉽게 섭취 가능함
-신속한 컨디션 회복 — 피로할 때 섭취 시 활력이 생기고 컨디션 회복에 도움이 됨
-정성스럽고 고급스러운 포장 — 포장 상태가 고급스러워 선물용으로 만족도가 높음</t>
+          <t>확실한 컨디션 회복 — 피로가 쌓였을 때 섭취하면 빠르게 컨디션을 회복하고 힘이 남
+작은 정제로 편한 목넘김 — 알약 크기가 크지 않아 목으로 넘기기 용이함
+선물용으로 우수한 패키지 — 포장 상태가 깔끔하고 고급스러워 생일 선물용으로 적합함</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>물 없이 먹는 젤리 타입 — 구미 형태라 물 없이 간편하게 섭취할 수 있어 매일 챙기기 쉬움
-맛있고 향긋한 풍미 — 맛과 향이 좋아 거부감 없이 맛있게 먹을 수 있음</t>
+          <t>체력 유지 및 피로 회복 — 운동 후나 야근 시 섭취하면 컨디션 회복과 훈련 집중도 향상에 도움 됨
+대용량 및 사은품 증정 — 30병의 넉넉한 양에 레몬샷 증정품까지 제공되어 알참</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>체력 관리 및 피로 회복 — 복용 후 피로가 줄고 컨디션과 훈련 집중도 유지에 도움이 됨
-대용량 구성 및 혜택 — 30병 대용량에 증정품까지 추가되어 든든함</t>
+          <t>맛있고 간편한 구미 제형 — 물 없이 간식처럼 섭취할 수 있고 쫄깃하며 맛이 좋음
+귀여운 포장 및 외관 — 제품 포장과 모양이 예뻐 부담 없이 선물하기에 좋음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 선물용 패키지 — 포장이 깔끔하고 고급스러워 가볍게 선물하기에 적합함
-새콤달콤하여 맛있는 맛 — 새콤하고 달콤한 오렌지 맛으로 맛있게 먹을 수 있음
-간편한 복용 및 피로 감소 — 복용 방식이 간편하고 마신 후 피로감이 줄어드는 느낌임</t>
+          <t>고급스러운 포장 디자인 — 패키지 포장이 정성스럽고 고급스러워 선물용으로 제격임
+새콤달콤 맛있는 액상 — 오렌지 맛의 새콤달콤한 액상으로 거부감 없이 간편하게 복용 가능함
+피로 감소 및 체력 회복 — 섭취 후 피로함이 줄어들고 활기찬 기분을 주는 데 도움 됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 액상과 비타민 젤리 — 맛이 새콤하고 개운하며 함께 증정된 비타민 젤리도 맛있음
-한 병으로 간편한 영양 보충 — 하루 한 병과 정제로 여러 영양소를 간편하고 휴대하기 쉽게 챙김
-속 더부룩함 없는 편안함 — 알약 크기가 적당하고 섭취 후 속이 불편한 느낌이 없음</t>
+          <t>간편한 휴대 및 올인원 섭취 — 한 병에 알약과 액상이 같이 있어 가방에 휴대하며 먹기 편리함
+개운한 맛과 편안한 속 — 맛이 새콤하고 개운하며 복용 후 속이 불편하지 않음
+고급 포장과 젤리 증정 — 포장이 깔끔하고 추가 동봉된 비타민 젤리가 맛있음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>우수한 피로 회복 효과 — 피로가 쌓였을 때 마시면 피로감이 줄어들고 몸에 활력이 생김
-맛있는 액상 비타민 — 섭취하기에 맛이 좋아 부담 없이 먹기 편함
-고급스러운 패키지와 증정품 — 추석 선물 패키지가 고급스럽고 젤리까지 추가되어 만족스러움</t>
+          <t>성별 맞춤 영양 설계 — 남성과 여성에 맞는 영양소로 구성되어 효율적인 관리가 가능함
+지속적인 활력 및 피로 완화 — 꾸준히 복용 시 피로가 감소하고 활력이 오래 지속됨
+선물 느낌의 깔끔한 포장 — 포장이 정성스럽고 깔끔하여 선물 받는 기분을 북돋아 줌</t>
         </is>
       </c>
     </row>
@@ -4157,20 +4190,24 @@
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>구매 직후 가격 인하 — 제품 수령 직후 판매 가격이 내려가 아쉬움이 남음</t>
+          <t>구매 직후 가격 하락 — 제품 구매 후 가격이 추가 할인되어 아쉬움이 남음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>배송 중 박스 훼손 — 배송 과정에서 제품 박스가 찢어진 상태로 전달됨</t>
-        </is>
-      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>배송 시 제품 박스 훼손 — 배송 중 포장 박스가 찢어져서 도착함</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>큰 알약 크기로 인한 불편 — 정제 크기가 커서 물로 삼킬 때 다소 부담스러움</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -4205,14 +4242,14 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
           <t>24,000원</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>52,900원</t>
-        </is>
-      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
           <t>33,000원</t>
@@ -4225,7 +4262,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>15,900원</t>
+          <t>59,800원</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4415,12 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -4435,19 +4472,19 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
           <t>한끼통살</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>그레인온</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
-        </is>
-      </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t>한끼통살</t>
@@ -4470,7 +4507,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>익스트림</t>
+          <t>뉴트리디데이</t>
         </is>
       </c>
     </row>
@@ -4492,19 +4529,19 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
           <t>[한끼통살] 닭가슴살 한달식단 패키지 30팩+(증정)보냉백</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>[리센느에디션] 베리말차 캡슐레이션 효소 1.8g 30포, 2개</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀효소G 3개월분+10포증정(총100포) + 파로저당씬칩 증정</t>
-        </is>
-      </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
           <t>[한끼통살] 단백질 든든형 닭가슴살 21일식단관리+ (증정)현미크리스피 닭가슴살 오리지널 1개</t>
@@ -4527,7 +4564,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>아메리카노 증정 에너지 활력선물 [김종국 추천세트]익스트림 아르기닌정 (2개월분) &amp; 밀크씨슬 플러스 (2개월분) + 쇼핑백 증정</t>
+          <t>"이게 바로 찐! 초고함량" 액상스틱 L-아르기닌 7000 3박스 [케이스 동봉]</t>
         </is>
       </c>
     </row>
@@ -4581,13 +4618,13 @@
         <v>1667</v>
       </c>
       <c r="E19" s="3" t="n">
+        <v>875</v>
+      </c>
+      <c r="F19" s="3" t="n">
         <v>147</v>
       </c>
-      <c r="F19" s="3" t="n">
+      <c r="G19" s="3" t="n">
         <v>93</v>
-      </c>
-      <c r="G19" s="3" t="n">
-        <v>875</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>52</v>
@@ -4602,7 +4639,7 @@
         <v>248</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>1534</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" ht="90" customHeight="1">
@@ -4613,103 +4650,115 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>매우 고급스러운 선물 포장 — 틴케이스, 보자기 등 핑크톤 포장이 섬세하고 고급스러움
-비리지 않고 맛있는 맛 — 비린 맛 없이 맛있게 먹을 수 있음
-피부 변화 및 만족도 — 섭취 후 피부가 탱탱해지고 맑아지는 느낌을 받음</t>
+          <t>정성스럽고 고급스러운 포장 — 보자기, 틴케이스, 핑크 박스 등 포장 구성이 예쁘고 고급스러움
+비리지 않고 맛있는 액상 — 콜라겐 특유의 비린 맛이 없고 맛이 뛰어남
+피부 개선 체감 효과 — 섭취 시 피부가 맑아지고 탱탱해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>소화 및 변비 개선 효과 — 속 거북함이 줄어들고 변비 증상이 개선되어 지속 복용함
-풍성한 구성과 저렴한 가격 — 덤 증정품과 함께 저렴한 가격으로 구매할 수 있어 만족스러움</t>
+          <t>소화 및 변비 개선 효과 — 소화 불량을 완화하고 변비 증상 개선에 큰 도움이 됨
+합리적인 가격과 사은품 — 가격이 착하고 추가 효소 사은품까지 풍성하게 증정됨
+고급스러운 선물 포장 — 선물 포장 상태가 깔끔하고 고급스러움</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>다양하고 맛있는 메뉴 구성 — 여러 가지 맛이 있어 질리지 않고 간편하게 먹을 수 있음
-실용적인 보냉백 증정 — 함께 증정되는 보냉파우치(도시락가방)가 유용함</t>
+          <t>뛰어난 소화 촉진 효과 — 식후 복용 시 소화가 잘 되며 소화력이 떨어진 사람에게 추천함
+우수한 가성비 — 저렴한 가격에 많은 수량을 구매할 수 있어 경제적임
+빠른 배송 및 예쁜 패키지 — 배송이 빠르고 선물하기 좋은 예쁜 포장으로 도착함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>기대를 뛰어넘는 맛있는 맛 — 말차를 잘 못 먹는 사람도 맛있게 먹을 수 있는 풍미임
-포토카드와 단백질바 사은품 — 리센느 원이 포토카드와 단백질 스낵이 함께 들어있어 만족스러움</t>
+          <t>다채롭고 맛있는 종류 구성 — 다양한 맛으로 구성되어 질리지 않고 맛있게 식단 관리가 가능함
+알찬 가성비 및 보냉백 증정 — 가격 대비 양이 많고 도시락용 보냉 파우치를 함께 증정함</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>우수한 소화 촉진 효과 — 식후 복용 시 소화가 잘 되어 소화력 개선에 큰 도움이 됨
-가성비 좋은 저렴한 가격 — 증정품 포함 알찬 구성을 저렴하게 구매할 수 있음</t>
+          <t>거부감 없는 맛있는 말차 맛 — 말차를 잘 못 먹는 사람도 맛있게 먹을 수 있으며 섭취가 간편함
+알찬 굿즈 및 사은품 — 포토카드와 단백질 바 증정 등 에디션 구성이 풍성함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>부드러운 식감과 뛰어난 맛 — 닭가슴살 특유의 뻑뻑함이 없고 맛이 자극적이지 않음
-매일 색다른 다양성 — 맛의 종류가 다채로워 다이어트 중에도 물리지 않음</t>
+          <t>부드러운 식감과 다양한 맛 — 닭가슴살이 뻑뻑하지 않고 부드러우며 다채로운 양념으로 물리지 않음
+저렴한 가격과 간편한 조리 — 구성 대비 가격이 착하고 전자레인지 조리로 간편함</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>텁텁함 없는 달콤한 맛 — 단백질 음료 특유의 비리고 텁텁한 맛 없이 진하고 달콤함
-속 편한 부드러운 목넘김 — 마신 후 속이 더부룩하지 않고 부드럽게 마실 수 있음
-휴대하기 편리한 디자인 — 슬림한 팩 형태로 가방에 들고 다니며 챙겨 마시기 편함</t>
+          <t>비린 맛 없는 달콤한 풍미 — 단백질 음료 특유의 텁텁함이나 비린 맛이 전혀 없고 맛있음
+부드러운 목넘김과 속 편안함 — 당이 낮고 부드러우며 마신 뒤 속 더부룩함이 적음
+휴대하기 편한 패키지 — 패키지가 슬림하여 가방에 휴대하며 운동 후나 간식으로 먹기 좋음</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 앰플 용기 디자인 — 용기와 포장이 고급스러워 공주님이 먹는 듯한 느낌을 줌
-먹기 편한 맛있는 풍미 — 맛이 있어 약 같은 거부감 없이 즐겁게 마실 수 있음</t>
+          <t>고급스럽고 예쁜 패키지 — 케이스와 병 디자인이 공주풍으로 예쁘고 고급스러워 선물용으로 좋음
+상큼하고 거부감 없는 맛 — 비타민 음료처럼 상큼하고 맛있어서 부담 없이 복용 가능함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>6200mg 초고함량 활력 제공 — 아르기닌 함량이 높아 운동 시 지구력과 활력 충전에 효과적임
-고급 선물 패키지와 추가 증정 — 전용 쇼핑백과 추가 5포 증정으로 선물용 완성도가 높음
-하루 1포 간편한 개별 포장 — 개별 포장되어 있어 가지고 다니며 언제든 먹기 편리함</t>
+          <t>초고함량으로 뛰어난 활력 제공 — 6200mg 고함량이라 운동 시 지구력 향상과 피로 회복에 효과적임
+휴대 및 섭취의 간편성 — 하루 1포 개별 포장으로 휴대 및 복용이 편함
+고급 포장과 추가 증정 — 전용 쇼핑백과 추가 증정 포가 구성되어 선물하기에 적합함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>아르기닌과 밀크씨슬의 조합 — 활력과 간 건강을 한 번에 챙길 수 있는 영양제 구성임
-피로 개선 및 체력 증진 — 아침에 일어날 때 몸이 가벼워지고 운동 수행 능력에 도움이 됨
-넉넉한 용량과 선물용 구성 — 2개월 분량에 쇼핑백까지 증정되어 선물하기에 적합함</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
+          <t>피로 회복 및 운동 체력 증진 — 복용 시 하루를 가볍게 시작할 수 있고 운동 수행 능력 향상에 도움 됨
+부담 없는 상큼한 레몬 맛 — 맛있는 레몬 맛이라 거부감 없이 맛있게 먹기 좋음
+외출 시 편한 액상 스틱 — 액상 스틱 제형이라 물 없이도 챙겨 먹기 쉽고 외출 시 휴대하기 용이함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
       <c r="B21" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>지속적인 가격 상승 — 제품 가격이 계속 인상되어 부담이 생김</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 아쉬움 — 지인 선물용으로 여러 개 구매하고 싶으나 구매 갯수 제한이 있음</t>
+          <t>구매 수량 제한의 아쉬움 — 지인 선물용으로 구매 시 수량 제한이 있어 불편함</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 포장 터짐 문제 — 일부 제품의 진공 포장이 헐렁하거나 터져서 소스가 흘러나옴</t>
+          <t>구매 갯수 제한 존재 — 대량 구매 시 갯수 제한이 설정되어 있어 아쉬움</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>포토카드 무작위 구성 미적용 — 포토카드가 랜덤 구성이 아닌 고정형으로 제공되어 아쉬움</t>
+          <t>포장 불량으로 인한 터짐 — 진공 포장이 헐렁하거나 봉지가 터져 소스가 묻어남
+증정 가방 크기 차이 — 사은품으로 받은 도시락 가방이 사진보다 실제 크기가 큼</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>구매 수량 제한의 불편함 — 선물용으로 대량 구매를 원하나 개수 제한이 설정되어 있음</t>
+          <t>포토카드 구성의 아쉬움 — 포토카드가 고정 디자인으로 제공되어 다소 아쉬움</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 제품 해동 상태 — 배송 과정에서 상품이 전부 녹은 상태로 수령됨</t>
+          <t>배송 시 제품 해동 상태 — 배송 과정에서 제품이 완전히 녹아서 도착함</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>진한 농도로 인한 섭취 느낌 — 액상이 다소 진하여 마신 후 물을 따로 마셔야 함
+단기 복용 시 미미한 효과 — 짧은 기간 복용 시에는 체감되는 효과가 다소 부족함</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
     </row>
@@ -4731,19 +4780,19 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
+          <t>19,900원</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
           <t>46,900원</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>24,900원</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>19,900원</t>
-        </is>
-      </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>33,000원</t>
@@ -4766,7 +4815,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>25,900원</t>
+          <t>30,900원</t>
         </is>
       </c>
     </row>
@@ -4956,7 +5005,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4964,51 +5013,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>1,000원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000281&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260504/H44oDYbaAQPekxvnTd9T600000281_00_01H44oDYbaAQPekxvnTd9T.png</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>1077</v>
+        <v>286</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>원활한 배변 활동에 도움 — 섭취 후 화장실을 쉽게 갈 수 있어 만족도가 높음</t>
+          <t>압도적인 가성비 — 하루 오백원 수준의 매우 저렴한 가격으로 비타민D 보충이 가능함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>뛰어난 가성비와 편의성 — 가격이 저렴하고 간편하게 마실 수 있어 체험용으로 좋음</t>
+          <t>깔끔한 디자인과 우수한 성능 — 디자인이 깔끔하고 누구나 편하게 복용하기에 좋음</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>위 부담감을 주는 강한 신맛 — 신맛이 매우 강하여 위가 약한 경우 주의가 필요함</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
@@ -5023,12 +5068,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>닥터블릿</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5038,39 +5083,43 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000139&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=031930043&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/Am2C7Da2wracg1TigkAF600000139_00_00Am2C7Da2wracg1TigkAF.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260106/ifUNcDpBRic8ZZffJeay031930043_00_03ifUNcDpBRic8ZZffJeay.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2295</v>
+        <v>1675</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>부담 없는 우수한 가성비 — 가격이 저렴하여 계속 복용하기에 부담이 없음</t>
+          <t>자연스러운 수면 유도 — 누워있을 때 자연스럽게 잠에 들도록 도움을 줌</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>빠른 배송과 높은 만족도 — 배송이 빠르고 재구매 의사가 높을 정도로 만족스러움</t>
+          <t>저렴한 가성비 — 고가의 타사 멜라토닌 제품과 동일 함량 대비 가격이 매우 저렴함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>약한 효과 및 새벽 깨어남 — 약 효과가 강하지 않아 복용 후 새벽에 깨는 현상이 발생함</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5078,7 +5127,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 루테인 지아잔틴 30캡슐</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5093,39 +5142,43 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953533&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=994953529&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250627/lXFnthJvrHdOJJvI4JC2994953533_00_00lXFnthJvrHdOJJvI4JC2.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250627/vXg1N5D0xbSNweDPvvl2994953529_00_00vXg1N5D0xbSNweDPvvl2.jpg</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>733</v>
+        <v>344</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>목넘김이 쉬운 초소형 캡슐 — 캡슐 크기가 매우 작아 약을 잘 넘기지 못하는 경우에도 편함</t>
+          <t>맛있는 석류 맛 — 석류 맛이 뛰어나며 찬물에 타서 맛있게 먹기 좋음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>눈 피로 완화 및 건조함 개선 — 섭취 후 눈이 덜 뻑뻑한 느낌이 들어 꾸준히 복용하기 좋음</t>
+          <t>피부 케어 체감 — 섭취 후 예뻐지고 몸이 가벼워지는 느낌을 줌</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>다소 진하고 느끼한 맛 — 맛의 농도가 매우 진해서 일부 느끼하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5133,43 +5186,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘B 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>동화약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618643&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/yaxFSMtpTnhrztKNOjGw601618643_00_00yaxFSMtpTnhrztKNOjGw.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
-        <v>567</v>
+        <v>6490</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>마그네슘과 비타민B 복합 — 마그네슘과 비타민 B를 동시에 챙길 수 있어 효율적임</t>
+          <t>부담 없는 가성비 — 착한 가격으로 항산화 건강을 꾸준히 관리할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>최고 수준의 가성비와 함량 — 영양 성분 함량이 좋고 가격 대비 구성이 만족스러움</t>
+          <t>빠른 배송 및 꾸준한 구매 — 배송이 빠르고 다이소에서 지속해서 구매해 먹기 편리함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -5180,7 +5233,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5188,12 +5241,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>오브맘</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5203,43 +5256,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250922/dxtu28UFPhWKbi5IG3n8613602130_00_01dxtu28UFPhWKbi5IG3n8.jpg</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>2647</v>
+        <v>1518</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>높은 가성비와 확실한 효과 — 가격이 착하고 필요한 비타민C 성분만 들어있어 효과적임</t>
+          <t>맛있는 자몽 맛 구미 — 상큼한 자몽 맛이라 간식처럼 즐기기 좋고 식욕 억제에 도움 됨</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>지속적인 재구매 만족도 — 부담 없이 꾸준히 사 먹기 적합함</t>
+          <t>복합 영양소 간편 섭취 — 비타민D와 아연을 젤리 형태로 한 번에 간편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>겉포장 상자 찌그러짐 — 배송 시 제품의 외곽 상자가 찌그러진 상태로 수령됨</t>
-        </is>
-      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
     </row>
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5247,54 +5296,54 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=913624075&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911213&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250519/2rLyPRrrXXN6XdvBMjj5913624075_00_002rLyPRrrXXN6XdvBMjj5.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260907/E3CpURjLLswf9MgzRChF610911213_00_01E3CpURjLLswf9MgzRChF.jpg</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>1001</v>
+        <v>37</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>맛있는 맛과 간편한 섭취 — 맛이 좋고 먹기가 편리하여 꾸준히 챙겨 먹기 적합함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>원활한 배변 활동 도움 — 다이어트 효과 외에 쾌변을 도와주는 기능이 만족스러움</t>
-        </is>
-      </c>
+          <t>귀여운 네이밍과 저렴한 가격 — 공주캔디라는 이름이 귀엽고 저렴하게 붓기 관리를 시도해 보기 좋음</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>맛에 대한 상대적 아쉬움 — 파인애플 맛에 비해 호박 맛 제품의 풍미가 조금 아쉬움</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5302,58 +5351,54 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>3,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602085&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000131&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260624/m6tznB24o1VYvw4vwVs3613602085_00_00m6tznB24o1VYvw4vwVs3.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/rCiQaBH4VQ1rKKr7rz83600000131_00_00rCiQaBH4VQ1rKKr7rz83.png</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2666</v>
+        <v>4672</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>과식 후 배변 활동 촉진 — 과식한 날 복용 시 장을 비워주어 화장실 가기가 원활함</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>효과적인 혈당 관리 — 야식이나 회식 후 섭취 시 혈당 스파이크 방지 및 관리에 도움 됨</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>저렴한 가성비와 빠른 배송 — 가격이 저렴하여 계속 재구매하기에 부담이 없고 배송이 빠름</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>다이어트 체감 효과 부족 — 체중 감량 효과는 직접적으로 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>묽은 배변 양상 발생 — 화장실 이용 시 묽은 상태의 배변이 유도됨</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5361,12 +5406,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>오브맘</t>
+          <t>익스트림</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5376,36 +5421,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=613602126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=987253276&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251015/CucIwXdPFflEtkJEtXZl613602126_00_01CucIwXdPFflEtkJEtXZl.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260422/qm625V7JKEa8Iu7GrFAf987253276_00_01qm625V7JKEa8Iu7GrFAf.jpg</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>4.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1295</v>
+        <v>628</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>챙겨 먹기 쉬운 구미 타입 — 젤리 형태라 귀찮지 않고 즐겁게 하루 한 알씩 먹을 수 있음</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>맛있는 풍미와 좋은 식감 — 식감과 맛이 훌륭하여 거부감 없이 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>눈 피로 개선 체감 — 섭취한 날과 안 먹은 날의 눈 상태 차이가 느껴짐</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>뛰어난 용량 대 가격 가성비 — 가격 대비 양이 넉넉하여 크레아틴을 부담 없이 섭취 가능함</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>생각보다 작은 용기 크기 — 실물 제품 용기의 사이즈가 예상보다 작음</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -5420,43 +5461,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
+          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>동화약품</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5,000원</t>
+          <t>2,000원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591555314&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=601618637&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260428/PgvB4Sjc4dtxAp5jXpwI591555314_00_01PgvB4Sjc4dtxAp5jXpwI.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260406/xHnNEgPvPnLilc6RIN7P601618637_00_00xHnNEgPvPnLilc6RIN7P.jpg</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.7</v>
       </c>
       <c r="J10" t="n">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>확실하고 빠른 배변 효과 — 변비나 속 답답함이 있을 때 마시면 장 청소 효과가 뛰어남</t>
+          <t>목 진정 및 환절기 건강 관리 — 목감기 기운이 있거나 추울 때 마시면 목이 편안해짐</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>저렴한 가격과 고가성비 — 다이소 특유의 매우 착한 가격대로 구매할 수 있음</t>
+          <t>휴대성과 뛰어난 가성비 — 가격대비 성능이 좋고 여행 시 상비약으로 휴대하기 편함</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -5467,7 +5508,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5475,43 +5516,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>종근당</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306201&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000148&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260406/NBw0phjtTvR7tEfBicGr032306201_00_01NBw0phjtTvR7tEfBicGr.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/a7ohwSe3ShJimhwztOOK600000148_00_00a7ohwSe3ShJimhwztOOK.png</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1216</v>
+        <v>3374</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>혈당 조절 및 다이어트 도움 — 혈당 관리가 되고 다이어트에도 소폭 도움이 됨</t>
+          <t>위생적인 개별 포장 — 알약이 개별 포장되어 있어 보관과 위생 면에서 만족스러움</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>배변 활동 원활에 도움 — 복용 후 화장실을 잘 가게 되어 만족함</t>
+          <t>부담 없는 가격 — 가격대비 영양 구성이 훌륭하여 만족스럽게 이용할 수 있음</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
@@ -5630,52 +5671,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민D</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>루테인/눈건강</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>비타민D</t>
         </is>
       </c>
     </row>
@@ -5687,52 +5728,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>자연관</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>닥터블릿</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>이너뷰 바이 리튠</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>이너뷰 바이 리튠</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>오브맘</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>익스트림</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>동화약품</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>대웅제약</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>닥터블릿</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>오브맘</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>종근당</t>
         </is>
       </c>
     </row>
@@ -5744,52 +5785,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
+          <t>대웅제약 비타민D 4000IU 10정 10일분</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 쏘팔메토 옥타코사놀 30캡슐 30일분</t>
+          <t>닥터블릿 멜라드림 30정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>LG생활건강 이너뷰 루테인 지아잔틴 30캡슐</t>
+          <t>LG생활건강 이너뷰 진한 레드 석류 콜라겐 7포</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>동화 바이마그랩 마그네슘B 30정 30일분</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민C 30정 30일분</t>
+          <t>오브맘 비타민D＆아연 하루구미 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 다이어트 홀릭 30포 15일분</t>
+          <t>[옥수수수염＆호박] 동국제약 맛있는 센텔라 공주캔디 20정 20일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7days 팻버닝 21캡슐</t>
+          <t>대웅제약 바나바잎 추출물 30정 30일분</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>오브맘 눈건강 루테인 하루구미 30일분</t>
+          <t>[우형재 PICK] 익스트림 모노크레아틴 플러스 120 g 40일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 락토조이 오늘비움 3병 3일분</t>
+          <t>동화 부채표 배도라지쌍화 5포 5일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>종근당 데일리와이즈 혈당컷 다이어트 12정 12일분</t>
+          <t>대웅제약 칼슘 마그네슘 비타민D 60정 30일분</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5847,7 @@
         <v>4.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.8</v>
@@ -5815,10 +5856,10 @@
         <v>4.8</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.8</v>
@@ -5827,7 +5868,7 @@
         <v>4.7</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -5837,37 +5878,37 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1077</v>
+        <v>286</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2295</v>
+        <v>1675</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>733</v>
+        <v>344</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>567</v>
+        <v>6490</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2647</v>
+        <v>1518</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1001</v>
+        <v>37</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2666</v>
+        <v>4672</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>1295</v>
+        <v>628</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>348</v>
+        <v>418</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>1216</v>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+        <v>3374</v>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>긍정리뷰</t>
@@ -5875,92 +5916,93 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>원활한 배변 활동에 도움 — 섭취 후 화장실을 쉽게 갈 수 있어 만족도가 높음
-뛰어난 가성비와 편의성 — 가격이 저렴하고 간편하게 마실 수 있어 체험용으로 좋음</t>
+          <t>압도적인 가성비 — 하루 오백원 수준의 매우 저렴한 가격으로 비타민D 보충이 가능함
+깔끔한 디자인과 우수한 성능 — 디자인이 깔끔하고 누구나 편하게 복용하기에 좋음</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 우수한 가성비 — 가격이 저렴하여 계속 복용하기에 부담이 없음
-빠른 배송과 높은 만족도 — 배송이 빠르고 재구매 의사가 높을 정도로 만족스러움</t>
+          <t>자연스러운 수면 유도 — 누워있을 때 자연스럽게 잠에 들도록 도움을 줌
+저렴한 가성비 — 고가의 타사 멜라토닌 제품과 동일 함량 대비 가격이 매우 저렴함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>목넘김이 쉬운 초소형 캡슐 — 캡슐 크기가 매우 작아 약을 잘 넘기지 못하는 경우에도 편함
-눈 피로 완화 및 건조함 개선 — 섭취 후 눈이 덜 뻑뻑한 느낌이 들어 꾸준히 복용하기 좋음</t>
+          <t>맛있는 석류 맛 — 석류 맛이 뛰어나며 찬물에 타서 맛있게 먹기 좋음
+피부 케어 체감 — 섭취 후 예뻐지고 몸이 가벼워지는 느낌을 줌</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>마그네슘과 비타민B 복합 — 마그네슘과 비타민 B를 동시에 챙길 수 있어 효율적임
-최고 수준의 가성비와 함량 — 영양 성분 함량이 좋고 가격 대비 구성이 만족스러움</t>
+          <t>부담 없는 가성비 — 착한 가격으로 항산화 건강을 꾸준히 관리할 수 있음
+빠른 배송 및 꾸준한 구매 — 배송이 빠르고 다이소에서 지속해서 구매해 먹기 편리함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>높은 가성비와 확실한 효과 — 가격이 착하고 필요한 비타민C 성분만 들어있어 효과적임
-지속적인 재구매 만족도 — 부담 없이 꾸준히 사 먹기 적합함</t>
+          <t>맛있는 자몽 맛 구미 — 상큼한 자몽 맛이라 간식처럼 즐기기 좋고 식욕 억제에 도움 됨
+복합 영양소 간편 섭취 — 비타민D와 아연을 젤리 형태로 한 번에 간편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>맛있는 맛과 간편한 섭취 — 맛이 좋고 먹기가 편리하여 꾸준히 챙겨 먹기 적합함
-원활한 배변 활동 도움 — 다이어트 효과 외에 쾌변을 도와주는 기능이 만족스러움</t>
+          <t>귀여운 네이밍과 저렴한 가격 — 공주캔디라는 이름이 귀엽고 저렴하게 붓기 관리를 시도해 보기 좋음</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>과식 후 배변 활동 촉진 — 과식한 날 복용 시 장을 비워주어 화장실 가기가 원활함</t>
+          <t>효과적인 혈당 관리 — 야식이나 회식 후 섭취 시 혈당 스파이크 방지 및 관리에 도움 됨
+저렴한 가성비와 빠른 배송 — 가격이 저렴하여 계속 재구매하기에 부담이 없고 배송이 빠름</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>챙겨 먹기 쉬운 구미 타입 — 젤리 형태라 귀찮지 않고 즐겁게 하루 한 알씩 먹을 수 있음
-맛있는 풍미와 좋은 식감 — 식감과 맛이 훌륭하여 거부감 없이 섭취 가능함
-눈 피로 개선 체감 — 섭취한 날과 안 먹은 날의 눈 상태 차이가 느껴짐</t>
+          <t>뛰어난 용량 대 가격 가성비 — 가격 대비 양이 넉넉하여 크레아틴을 부담 없이 섭취 가능함</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>확실하고 빠른 배변 효과 — 변비나 속 답답함이 있을 때 마시면 장 청소 효과가 뛰어남
-저렴한 가격과 고가성비 — 다이소 특유의 매우 착한 가격대로 구매할 수 있음</t>
+          <t>목 진정 및 환절기 건강 관리 — 목감기 기운이 있거나 추울 때 마시면 목이 편안해짐
+휴대성과 뛰어난 가성비 — 가격대비 성능이 좋고 여행 시 상비약으로 휴대하기 편함</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>혈당 조절 및 다이어트 도움 — 혈당 관리가 되고 다이어트에도 소폭 도움이 됨
-배변 활동 원활에 도움 — 복용 후 화장실을 잘 가게 되어 만족함</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="60" customHeight="1">
+          <t>위생적인 개별 포장 — 알약이 개별 포장되어 있어 보관과 위생 면에서 만족스러움
+부담 없는 가격 — 가격대비 영양 구성이 훌륭하여 만족스럽게 이용할 수 있음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>위 부담감을 주는 강한 신맛 — 신맛이 매우 강하여 위가 약한 경우 주의가 필요함</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>약한 효과 및 새벽 깨어남 — 약 효과가 강하지 않아 복용 후 새벽에 깨는 현상이 발생함</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>다소 진하고 느끼한 맛 — 맛의 농도가 매우 진해서 일부 느끼하게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>겉포장 상자 찌그러짐 — 배송 시 제품의 외곽 상자가 찌그러진 상태로 수령됨</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr"/>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>다이어트 체감 효과 부족 — 체중 감량 효과는 직접적으로 체감하기 어려움
-묽은 배변 양상 발생 — 화장실 이용 시 묽은 상태의 배변이 유도됨</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>맛에 대한 상대적 아쉬움 — 파인애플 맛에 비해 호박 맛 제품의 풍미가 조금 아쉬움</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>생각보다 작은 용기 크기 — 실물 제품 용기의 사이즈가 예상보다 작음</t>
+        </is>
+      </c>
       <c r="K9" s="3" t="inlineStr"/>
       <c r="L9" s="3" t="inlineStr"/>
     </row>
@@ -5972,52 +6014,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
+          <t>1,000원</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>5,000원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>3,000원</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>3,000원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>2,000원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>5,000원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>5,000원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>2,000원</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6238,7 @@
     <row r="2" ht="38" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6204,27 +6246,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>바이너랩 겟글로시 글루타치온 30포(리포솜)(15일분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>바이너랩</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48,000원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000167142&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0016/A00000016714210ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -6239,7 +6281,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6247,39 +6289,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>올더베러 웰니스 구미 30일분 택1</t>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>올더베러</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9,200원</t>
+          <t>31,400원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000202658&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587419ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020265829ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>간식 같은 맛있는 풍미 — 레몬라임, 복숭아 맛 등의 구미로 맛있게 즐길 수 있음</t>
+          <t>매력적인 굿즈 증정 행사 — 카카오 키링 및 포토카드 등 특별 사은품 구성으로 만족감이 높음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>물 없이 간편한 루틴 생성 — 언제 어디서나 물 없이 바로 먹을 수 있어 루틴 형성이 쉬움</t>
+          <t>간편한 1일 1캡슐 복용 — 아침 빈속에 한 알씩 섭취하기 편리함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
@@ -6290,7 +6332,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6298,51 +6340,51 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>59,000원</t>
+          <t>12,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014347ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>374</v>
+        <v>12581</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>질과 장을 함께 케어 — 식약처 인정 원료로 질 건강과 장 건강을 한 번에 관리함</t>
+          <t>귀여운 산리오 콜라보 굿즈 — 태닝 러기지택 등 콜라보 증정품이 소장 가치가 높음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>목넘김이 편한 작은 캡슐 — 캡슐 사이즈가 작아서 아침에 삼키기 부담이 없음</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>만족스러운 캐릭터 협업 굿즈 — 포켓몬 에디션 카드케이스 등 증정품 구성이 유용함</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>배 아픔 없는 속 편한 유산균 — 복통이나 가스 차는 증상 없이 화장실을 편하게 갈 수 있음</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 사이즈 — 기존에 복용하던 제품에 비해 알약 크기가 살짝 크게 느껴짐</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
     </row>
@@ -6357,39 +6399,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+          <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>멜라메이트</t>
+          <t>올더베러</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16,900원</t>
+          <t>9,200원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000245874&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024587419ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>신속하고 깊은 수면 유도 — 자기 전 섭취 시 신속하게 잠에 들고 푹 잘 수 있음</t>
+          <t>맛있는 상큼한 구미 형태 — 레몬라임 맛의 젤리 형태로 간식처럼 맛있게 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>맛있고 간편한 젤리 형태 — 정제 약 형태가 아닌 젤리 타입이라 편하게 섭취 가능함</t>
+          <t>물 없이 편한 섭취 및 합리적 가격 — 물 없이 어디서나 먹을 수 있으며 세일 기간 가격이 합리적임</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
@@ -6400,7 +6442,7 @@
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -6408,33 +6450,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>코자아</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32,900원</t>
+          <t>30,400원</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000236755&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000206861&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023675540ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020686148ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>알찬 1+1 기획 구성 — 기획 구성이라 넉넉한 수량을 저렴하게 챙겨두기 좋음</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>장 건강 및 면역력 관리 — 아침 공복에 복용하여 장 건강과 면역력을 높이는 데 효과적임</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -6443,7 +6493,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6451,46 +6501,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
+          <t>[선물세트] 덴프스 덴마크 유산균이야기 2박스/4개월분 +쇼핑백 증정</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>빌드</t>
+          <t>덴프스</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>18,900원</t>
+          <t>52,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000219379&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=B000000140139&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0021/A00000021937922ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0014/B00000014013926ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>고소하고 맛있는 인절미 맛 — 쿰쿰한 냄새가 없고 고소한 인절미 풍미라 맛이 우수함</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>부드러운 고운 입자 제형 — 효소 입자가 매우 고와 목걸림 없이 섭취하기 편리함</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>식단 관리 및 체중 조절 도움 — 탄수화물 섭취 후나 다이어트 시 복용하기 좋음</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -6498,7 +6536,7 @@
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>프로바이오틱스/유산균</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -6506,27 +6544,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>지노마스터</t>
+          <t>프로뉴트리션</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>27,400원</t>
+          <t>39,800원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6541,7 +6579,7 @@
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -6549,31 +6587,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
+          <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>푸드올로지</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>22,900원</t>
+          <t>59,000원</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000175634&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249509&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=8</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0017/A00000017563462ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024950901ko.png?l=ko</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>374</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -6584,7 +6626,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6592,48 +6634,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>지노마스터</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42,900원</t>
+          <t>27,400원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000225938&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000244929&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022593803ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="J10" t="n">
-        <v>22131</v>
-      </c>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024492930ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>600정 대용량과 고가성비 — 넉넉한 20개월 대용량 구성이라 가격 대비 경제적임</t>
+          <t>매우 작은 캡슐 사이즈 — 170mg의 아주 작은 크기라 목넘김이 매우 편함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>원료와 브랜드 신뢰성 — 영국산 비타민C 원료를 사용해 믿고 장기 복용할 수 있음</t>
+          <t>질과 장의 동시 더블케어 — 기능성 원료로 질 건강과 장 건강을 함께 챙길 수 있음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>위생적인 개별 포장 방식 — 개별 PTP 포장으로 되어 있어 휴대가 편리하고 위생적임</t>
+          <t>귀여운 포켓몬 콜라보 굿즈 — 카드케이스 등 귀엽고 실용적인 굿즈가 함께 제공됨</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -6643,7 +6681,7 @@
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6651,35 +6689,51 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>프로뉴트리션</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>39,800원</t>
+          <t>16,900원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000205496&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020549614ko.jpg?l=ko</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15160</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>부담 없는 젤리 제형 — 맛있는 젤리 형태라 취침 전 부담 없이 맛있게 먹기 좋음</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>확실한 수면 질 개선 — 복용 시 뒤척임 없이 깊고 편안하게 잠에 들 수 있음</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>취침 전 추가 양치 필요 — 젤리 형태라 취침 직전에 먹은 후 다시 양치를 해야 하는 불편함이 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6794,52 +6848,52 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>다이어트/체중관리</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>프로바이오틱스/유산균</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
         </is>
       </c>
     </row>
@@ -6851,52 +6905,52 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>바이너랩</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>바이오코어유산균</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>올더베러</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>덴프스</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>프로뉴트리션</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>지노마스터</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>멜라메이트</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>코자아</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>빌드</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>푸드올로지</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>프로뉴트리션</t>
         </is>
       </c>
     </row>
@@ -6908,52 +6962,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>바이너랩 겟글로시 글루타치온 30포(리포솜)(15일분)</t>
+          <t>고려은단 비타민C1000 600정 (20개월분)</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>덴프스 덴마크 유산균이야기 우먼 2개월분(질유산균) + 철분 헤모케어 3포 증정</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
           <t>올더베러 웰니스 구미 30일분 택1</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[덴프스] 덴마크 유산균이야기 30캡슐 1+1 기획 (+트루바이타민 3포 증정)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[선물세트] 덴프스 덴마크 유산균이야기 2박스/4개월분 +쇼핑백 증정</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>[올영단독] 지노마스터 질유산균 70캡슐 (70일분)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>코자아 식물성 멜라토닌 함유 젤리/드링크 (단품/기획)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>[저분자] 빌드 프리미엄 테프 발효 효소 30포 (1개월분)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>지노마스터 질유산균 30캡슐 기획 (+보라지유 5일분) (1개월분)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[서현PICK] 콜레올로지 PRO 600mg*30정/60정 (15/30일분)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>고려은단 비타민C1000 600정 (20개월분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[한선화 PICK] 프로뉴트리션 듀얼플랜 다이어트 유산균 14포</t>
         </is>
       </c>
     </row>
@@ -6966,17 +7020,19 @@
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="3" t="inlineStr"/>
       <c r="E6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="3" t="inlineStr"/>
       <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="n">
+      <c r="J6" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="L6" s="3" t="inlineStr"/>
+      <c r="K6" s="3" t="inlineStr"/>
+      <c r="L6" s="3" t="n">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -6987,17 +7043,19 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="3" t="n">
-        <v>374</v>
+        <v>12581</v>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
       <c r="G7" s="3" t="inlineStr"/>
       <c r="H7" s="3" t="inlineStr"/>
       <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="n">
-        <v>22131</v>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+      <c r="J7" s="3" t="n">
+        <v>374</v>
+      </c>
+      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n">
+        <v>15160</v>
+      </c>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
@@ -7008,41 +7066,44 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>간식 같은 맛있는 풍미 — 레몬라임, 복숭아 맛 등의 구미로 맛있게 즐길 수 있음
-물 없이 간편한 루틴 생성 — 언제 어디서나 물 없이 바로 먹을 수 있어 루틴 형성이 쉬움</t>
+          <t>매력적인 굿즈 증정 행사 — 카카오 키링 및 포토카드 등 특별 사은품 구성으로 만족감이 높음
+간편한 1일 1캡슐 복용 — 아침 빈속에 한 알씩 섭취하기 편리함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>질과 장을 함께 케어 — 식약처 인정 원료로 질 건강과 장 건강을 한 번에 관리함
-목넘김이 편한 작은 캡슐 — 캡슐 사이즈가 작아서 아침에 삼키기 부담이 없음
-만족스러운 캐릭터 협업 굿즈 — 포켓몬 에디션 카드케이스 등 증정품 구성이 유용함</t>
+          <t>귀여운 산리오 콜라보 굿즈 — 태닝 러기지택 등 콜라보 증정품이 소장 가치가 높음
+배 아픔 없는 속 편한 유산균 — 복통이나 가스 차는 증상 없이 화장실을 편하게 갈 수 있음</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>신속하고 깊은 수면 유도 — 자기 전 섭취 시 신속하게 잠에 들고 푹 잘 수 있음
-맛있고 간편한 젤리 형태 — 정제 약 형태가 아닌 젤리 타입이라 편하게 섭취 가능함</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>고소하고 맛있는 인절미 맛 — 쿰쿰한 냄새가 없고 고소한 인절미 풍미라 맛이 우수함
-부드러운 고운 입자 제형 — 효소 입자가 매우 고와 목걸림 없이 섭취하기 편리함
-식단 관리 및 체중 조절 도움 — 탄수화물 섭취 후나 다이어트 시 복용하기 좋음</t>
-        </is>
-      </c>
+          <t>맛있는 상큼한 구미 형태 — 레몬라임 맛의 젤리 형태로 간식처럼 맛있게 섭취 가능함
+물 없이 편한 섭취 및 합리적 가격 — 물 없이 어디서나 먹을 수 있으며 세일 기간 가격이 합리적임</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>알찬 1+1 기획 구성 — 기획 구성이라 넉넉한 수량을 저렴하게 챙겨두기 좋음
+장 건강 및 면역력 관리 — 아침 공복에 복용하여 장 건강과 면역력을 높이는 데 효과적임</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>600정 대용량과 고가성비 — 넉넉한 20개월 대용량 구성이라 가격 대비 경제적임
-원료와 브랜드 신뢰성 — 영국산 비타민C 원료를 사용해 믿고 장기 복용할 수 있음
-위생적인 개별 포장 방식 — 개별 PTP 포장으로 되어 있어 휴대가 편리하고 위생적임</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>매우 작은 캡슐 사이즈 — 170mg의 아주 작은 크기라 목넘김이 매우 편함
+질과 장의 동시 더블케어 — 기능성 원료로 질 건강과 장 건강을 함께 챙길 수 있음
+귀여운 포켓몬 콜라보 굿즈 — 카드케이스 등 귀엽고 실용적인 굿즈가 함께 제공됨</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>부담 없는 젤리 제형 — 맛있는 젤리 형태라 취침 전 부담 없이 맛있게 먹기 좋음
+확실한 수면 질 개선 — 복용 시 뒤척임 없이 깊고 편안하게 잠에 들 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="B9" s="1" t="inlineStr">
@@ -7052,14 +7113,22 @@
       </c>
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr"/>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 사이즈 — 기존에 복용하던 제품에 비해 알약 크기가 살짝 크게 느껴짐</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>취침 전 추가 양치 필요 — 젤리 형태라 취침 직전에 먹은 후 다시 양치를 해야 하는 불편함이 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7069,52 +7138,52 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>48,000원</t>
+          <t>42,900원</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>31,400원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>12,900원</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
           <t>9,200원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>30,400원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>52,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>39,800원</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>59,000원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>27,400원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>16,900원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>32,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>18,900원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>27,400원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>22,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>42,900원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>39,800원</t>
         </is>
       </c>
     </row>
@@ -7244,25 +7313,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -7272,35 +7341,35 @@
         <v>22.5</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7310,10 +7379,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -7322,7 +7391,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -7332,16 +7401,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -7350,20 +7419,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>비타민D</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -7376,16 +7445,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -7394,7 +7463,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="B9" t="n">
